--- a/output/2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,6 @@
           <t>Željezara Krom</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Bjelovar, Bjelovarsko-bilogorska županija</t>
@@ -653,8 +652,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Ferramenta: utensili manuali ed elettrici, materiale per saldatura, dispositivi di protezione, abrasivi, viteria. Esistenza confermata (mojkvart.hr, Facebook), Trg Hrvatskih Branitelja 21. Contatti diretti non confermabili con certezza, lasciati vuoti.</t>
@@ -662,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -672,7 +669,6 @@
           <t>LEŽAJ d.o.o. (negozio al dettaglio a marchio LAGER)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Bjelovar, Bjelovarsko-bilogorska županija</t>
@@ -683,8 +679,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Ingrosso/dettaglio cuscinetti (ležajevi) e componenti metallici per industria e agricoltura. Attenzione: omonimia con diversa società LAGER d.o.o. cancellata dal registro (non confondere). Contatti diretti non confermabili con certezza, lasciati vuoti.</t>
@@ -692,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_17_Croazia_Bjelovarsko-bilogorska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Filiale rete vendita Würth, distribuzione utensili industriali, fissaggi e attrezzature per officina. Ulica Ferde Rusana 12, Bjelovar.</t>
+          <t>Filiale rete vendita Würth, distribuzione utensili industriali, fissaggi e attrezzature per officina. Ulica Ferde Rusana 12, Bjelovar. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
